--- a/artfynd/A 2308-2025 artfynd.xlsx
+++ b/artfynd/A 2308-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130699692</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2025 artfynd.xlsx
+++ b/artfynd/A 2308-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130699692</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2025 artfynd.xlsx
+++ b/artfynd/A 2308-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130699692</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2025 artfynd.xlsx
+++ b/artfynd/A 2308-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130699692</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -769,6 +769,208 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130699657</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stormyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>744953</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7225395</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130699572</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stormyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>744936</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7225403</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 2308-2025 artfynd.xlsx
+++ b/artfynd/A 2308-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130699692</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130699657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130699572</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>